--- a/AtchisonRegime/Outputs/Aust/ASX300_Communication/df_regSettingsASX300_Communication.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Communication/df_regSettingsASX300_Communication.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2700,7 +2700,7 @@
         <v>-0.9726698406613064</v>
       </c>
       <c r="C69" t="n">
-        <v>0.1460332201527155</v>
+        <v>0.1241894196525952</v>
       </c>
       <c r="D69" t="b">
         <v>0</v>
@@ -2733,7 +2733,7 @@
         <v>-0.930850647666511</v>
       </c>
       <c r="C70" t="n">
-        <v>0.2388191536463469</v>
+        <v>0.2339228301603335</v>
       </c>
       <c r="D70" t="b">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>-0.8890737992235942</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2406013064670542</v>
+        <v>0.2370619522653315</v>
       </c>
       <c r="D71" t="b">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>-1.090435517906162</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2007569734303624</v>
+        <v>0.1988546216055985</v>
       </c>
       <c r="D72" t="b">
         <v>0</v>
@@ -2832,7 +2832,7 @@
         <v>-1.28973601261699</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1400914415231331</v>
+        <v>0.1425534339131948</v>
       </c>
       <c r="D73" t="b">
         <v>0</v>
@@ -2865,7 +2865,7 @@
         <v>-1.487030325470401</v>
       </c>
       <c r="C74" t="n">
-        <v>0.08697420027797154</v>
+        <v>0.0881118604449648</v>
       </c>
       <c r="D74" t="b">
         <v>0</v>
@@ -2898,7 +2898,7 @@
         <v>-1.508648286865362</v>
       </c>
       <c r="C75" t="n">
-        <v>0.04458779450515634</v>
+        <v>0.05049734109636209</v>
       </c>
       <c r="D75" t="b">
         <v>0</v>
@@ -2931,7 +2931,7 @@
         <v>-1.530614951002829</v>
       </c>
       <c r="C76" t="n">
-        <v>0.03030594341745388</v>
+        <v>0.05226649969174183</v>
       </c>
       <c r="D76" t="b">
         <v>0</v>
@@ -2964,7 +2964,7 @@
         <v>-1.552867908392353</v>
       </c>
       <c r="C77" t="n">
-        <v>0.04619714416039293</v>
+        <v>0.06685384186450997</v>
       </c>
       <c r="D77" t="b">
         <v>0</v>
@@ -2997,7 +2997,7 @@
         <v>-1.4620752903488</v>
       </c>
       <c r="C78" t="n">
-        <v>0.03127296425735279</v>
+        <v>0.0775006846619135</v>
       </c>
       <c r="D78" t="b">
         <v>0</v>
@@ -3027,10 +3027,10 @@
         <v>45747</v>
       </c>
       <c r="B79" t="n">
-        <v>-1.380584681996217</v>
+        <v>-1.383605099136776</v>
       </c>
       <c r="C79" t="n">
-        <v>0.04765921338260101</v>
+        <v>0.09199325928623918</v>
       </c>
       <c r="D79" t="b">
         <v>0</v>
@@ -3050,6 +3050,39 @@
         </is>
       </c>
       <c r="I79" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B80" t="n">
+        <v>-1.312657793185081</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.08562355455682437</v>
+      </c>
+      <c r="D80" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-3.37679311857956</v>
+      </c>
+      <c r="G80" t="n">
+        <v>160755.36993514</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
         <is>
           <t>Type 1</t>
         </is>
